--- a/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:16:44+00:00</t>
+    <t>2025-02-11T12:34:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:34:01+00:00</t>
+    <t>2025-02-11T13:39:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -806,7 +806,7 @@
     <t>Madison</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J84-DepartementOM-RASS/FHIR/JDV-J84-DepartementOM-RASS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J258-Departement/FHIR/JDV-J258-Departement</t>
   </si>
   <si>
     <t>XAD.9</t>
@@ -1271,7 +1271,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="39.6640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="92.66015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="81.51953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:39:54+00:00</t>
+    <t>2025-02-11T16:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -883,7 +883,7 @@
     <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J74-Pays-RASS/FHIR/JDV-J74-Pays-RASS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J256-Pays/FHIR/JDV-J256-Pays</t>
   </si>
   <si>
     <t>XAD.6</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:00:38+00:00</t>
+    <t>2025-02-11T16:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:22:40+00:00</t>
+    <t>2025-02-12T08:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T08:22:12+00:00</t>
+    <t>2025-02-12T08:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T08:44:28+00:00</t>
+    <t>2025-02-12T08:52:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
